--- a/test/fixtures/xlsx/key-types/key-types.xlsx
+++ b/test/fixtures/xlsx/key-types/key-types.xlsx
@@ -15,21 +15,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="61">
-  <si>
-    <t xml:space="preserve">~~enum:Slot~~</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="63">
+  <si>
+    <t xml:space="preserve">:enum Slot</t>
   </si>
   <si>
     <t xml:space="preserve">Where a piece of equipment goes.</t>
   </si>
   <si>
-    <t xml:space="preserve">name</t>
+    <t xml:space="preserve">:field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">label</t>
   </si>
   <si>
     <t xml:space="preserve">value</t>
   </si>
   <si>
-    <t xml:space="preserve">description</t>
+    <t xml:space="preserve">desc</t>
   </si>
   <si>
     <t xml:space="preserve">None</t>
@@ -68,48 +71,51 @@
     <t xml:space="preserve">worn on the feet</t>
   </si>
   <si>
-    <t xml:space="preserve">~~table:Asset~~</t>
+    <t xml:space="preserve">:table Asset</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed by a uuid, which is what a pipeline that mints ids hands over.</t>
   </si>
   <si>
+    <t xml:space="preserve">:type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:target</t>
+  </si>
+  <si>
     <t xml:space="preserve">index</t>
   </si>
   <si>
+    <t xml:space="preserve">uuid</t>
+  </si>
+  <si>
     <t xml:space="preserve">primary index, a uuid</t>
   </si>
   <si>
-    <t xml:space="preserve">uuid</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
     <t xml:space="preserve">cs</t>
   </si>
   <si>
     <t xml:space="preserve">Path</t>
   </si>
   <si>
+    <t xml:space="preserve">string</t>
+  </si>
+  <si>
     <t xml:space="preserve">anything</t>
   </si>
   <si>
-    <t xml:space="preserve">string</t>
-  </si>
-  <si>
     <t xml:space="preserve">*Slot</t>
   </si>
   <si>
+    <t xml:space="preserve">Slot</t>
+  </si>
+  <si>
     <t xml:space="preserve">secondary index, an enum label</t>
   </si>
   <si>
-    <t xml:space="preserve">enum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slot</t>
-  </si>
-  <si>
     <t xml:space="preserve">3f2504e0-4f89-11d3-9a0c-0305e82c3301</t>
   </si>
   <si>
@@ -128,18 +134,18 @@
     <t xml:space="preserve">art/boots.fbx</t>
   </si>
   <si>
-    <t xml:space="preserve">~~table:Ledger~~</t>
+    <t xml:space="preserve">:table Ledger</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed by a bigint, for ids that outgrew 32 bits.</t>
   </si>
   <si>
+    <t xml:space="preserve">bigint</t>
+  </si>
+  <si>
     <t xml:space="preserve">primary index, past 32 bits</t>
   </si>
   <si>
-    <t xml:space="preserve">bigint</t>
-  </si>
-  <si>
     <t xml:space="preserve">Amount</t>
   </si>
   <si>
@@ -173,7 +179,7 @@
     <t xml:space="preserve">2f2504e0-4f89-11d3-9a0c-0305e82c3303</t>
   </si>
   <si>
-    <t xml:space="preserve">~~table:Slotting~~</t>
+    <t xml:space="preserve">:table Slotting</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed by an enum: one row per label, which is a shape sheets have.</t>
@@ -242,72 +248,73 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="B2:D8"/>
+  <dimension ref="B2:E7"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
       <c r="B2" t="s">
         <v>0</v>
       </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="B3" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" t="s">
-        <v>2</v>
-      </c>
       <c r="C4" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" t="s">
-        <v>5</v>
-      </c>
       <c r="C5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>7</v>
+        <v>10</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" t="s">
-        <v>8</v>
-      </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" t="s">
-        <v>11</v>
-      </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" t="s">
         <v>16</v>
+      </c>
+      <c r="E7" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -317,105 +324,104 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="B2:D11"/>
+  <dimension ref="B2:E9"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
       <c r="B2" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" t="s">
-        <v>18</v>
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
         <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="E4" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
         <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="E5" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
         <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" t="s">
-        <v>22</v>
-      </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>34</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" t="s">
-        <v>23</v>
-      </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>36</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="s">
-        <v>31</v>
-      </c>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" t="s">
-        <v>14</v>
+        <v>38</v>
+      </c>
+      <c r="E9" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -425,105 +431,104 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="B2:D11"/>
+  <dimension ref="B2:E9"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
       <c r="B2" t="s">
-        <v>37</v>
+        <v>39</v>
+      </c>
+      <c r="C2" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" t="s">
-        <v>38</v>
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
         <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>29</v>
+      </c>
+      <c r="E5" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" t="s">
-        <v>22</v>
-      </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>48</v>
+      </c>
+      <c r="E7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" t="s">
-        <v>23</v>
-      </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>51</v>
+      </c>
+      <c r="E8" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="s">
-        <v>45</v>
-      </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10" t="s">
-        <v>49</v>
-      </c>
-      <c r="D10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" t="s">
-        <v>51</v>
+        <v>7</v>
+      </c>
+      <c r="E9" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -533,105 +538,104 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="B2:D11"/>
+  <dimension ref="B2:E9"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
       <c r="B2" t="s">
-        <v>52</v>
+        <v>54</v>
+      </c>
+      <c r="C2" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" t="s">
-        <v>53</v>
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E3" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>44</v>
+      </c>
+      <c r="E4" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>29</v>
+      </c>
+      <c r="E5" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" t="s">
-        <v>30</v>
-      </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>10</v>
+      </c>
+      <c r="E7" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" t="s">
-        <v>23</v>
-      </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>16</v>
+      </c>
+      <c r="E8" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="s">
-        <v>8</v>
-      </c>
       <c r="C9" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" t="s">
-        <v>60</v>
+        <v>13</v>
+      </c>
+      <c r="E9" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
